--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484334_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484334_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. MARKOVETSKYY</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.0076</v>
+        <v>8.6271</v>
       </c>
       <c r="E2" t="n">
-        <v>9.091100000000001</v>
+        <v>7.8531</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0835</v>
+        <v>0.7739</v>
       </c>
       <c r="G2" t="n">
-        <v>3.476</v>
+        <v>4.7466</v>
       </c>
       <c r="H2" t="n">
-        <v>3.868</v>
+        <v>5.6905</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.392</v>
+        <v>-0.9439</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8497</v>
+        <v>5.6508</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5664</v>
+        <v>5.6498</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2833</v>
+        <v>0.001</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3737</v>
+        <v>-0.9042</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6984</v>
+        <v>0.0407</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6753</v>
+        <v>-0.9449</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>4.0087</v>
+        <v>0.0172</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4999</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5088</v>
+        <v>-0.0799</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7182</v>
+        <v>2.1052</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7182</v>
+        <v>2.1052</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1335</v>
+        <v>7.2644</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7409</v>
+        <v>8.4831</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3926</v>
+        <v>-1.2188</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7466</v>
+        <v>8.492599999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6905</v>
+        <v>3.7583</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9439</v>
+        <v>4.7343</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6508</v>
+        <v>9.4665</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6498</v>
+        <v>4.4615</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001</v>
+        <v>5.0049</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9042</v>
+        <v>-0.9739</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0407</v>
+        <v>-0.7032</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9449</v>
+        <v>-0.2706</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4763</v>
+        <v>0.2909</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0151</v>
+        <v>0.3255</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4612</v>
+        <v>-0.0345</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1052</v>
+        <v>-2.1052</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1052</v>
+        <v>-0.3321</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>V. MARKOVETSKYY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9615</v>
+        <v>6.7129</v>
       </c>
       <c r="E4" t="n">
-        <v>7.3709</v>
+        <v>7.0688</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4094</v>
+        <v>-0.3558</v>
       </c>
       <c r="G4" t="n">
-        <v>8.492599999999999</v>
+        <v>3.476</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7583</v>
+        <v>3.868</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7343</v>
+        <v>-0.392</v>
       </c>
       <c r="J4" t="n">
-        <v>9.4665</v>
+        <v>4.8497</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4615</v>
+        <v>4.5664</v>
       </c>
       <c r="L4" t="n">
-        <v>5.0049</v>
+        <v>0.2833</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9739</v>
+        <v>-1.3737</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7032</v>
+        <v>-0.6984</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2706</v>
+        <v>-0.6753</v>
       </c>
       <c r="P4" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.012</v>
+        <v>1.714</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7868000000000001</v>
+        <v>1.4776</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2252</v>
+        <v>0.2365</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.1052</v>
+        <v>1.7182</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3321</v>
+        <v>1.7182</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.0538</v>
+        <v>4.1864</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9654</v>
+        <v>4.5609</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0885</v>
+        <v>-0.3745</v>
       </c>
       <c r="G5" t="n">
         <v>2.716</v>
@@ -844,13 +844,13 @@
         <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5016</v>
+        <v>0.6341</v>
       </c>
       <c r="T5" t="n">
-        <v>0.743</v>
+        <v>0.3385</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.2956</v>
       </c>
       <c r="V5" t="n">
         <v>0.0549</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.7596</v>
+        <v>4.0163</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2409</v>
+        <v>1.4432</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5187</v>
+        <v>2.5731</v>
       </c>
       <c r="G6" t="n">
         <v>4.5006</v>
@@ -922,13 +922,13 @@
         <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3819</v>
+        <v>-0.1252</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4099</v>
+        <v>-0.2077</v>
       </c>
       <c r="U6" t="n">
-        <v>0.028</v>
+        <v>0.0824</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5545</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6827</v>
+        <v>3.0871</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8105</v>
+        <v>1.2149</v>
       </c>
       <c r="F7" t="n">
         <v>1.8722</v>
@@ -1000,10 +1000,10 @@
         <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1761</v>
+        <v>0.2283</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3026</v>
+        <v>0.1018</v>
       </c>
       <c r="U7" t="n">
         <v>0.1265</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2733</v>
+        <v>0.9197</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3281</v>
+        <v>-3.1371</v>
       </c>
       <c r="F8" t="n">
-        <v>4.6014</v>
+        <v>4.0567</v>
       </c>
       <c r="G8" t="n">
         <v>1.3418</v>
@@ -1078,13 +1078,13 @@
         <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>1.67</v>
+        <v>0.3164</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7567</v>
+        <v>-0.0522</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9133</v>
+        <v>0.3686</v>
       </c>
       <c r="V8" t="n">
         <v>1.6056</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9081</v>
+        <v>0.842</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2612</v>
+        <v>-1.4635</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1693</v>
+        <v>2.3055</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8005</v>
@@ -1156,13 +1156,13 @@
         <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0495</v>
+        <v>-0.1155</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2642</v>
+        <v>0.062</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3137</v>
+        <v>-0.1775</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3739</v>
+        <v>-0.5609</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2173</v>
+        <v>-0.8129</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1566</v>
+        <v>0.2519</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7904</v>
@@ -1234,13 +1234,13 @@
         <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4347</v>
+        <v>0.3783</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0522</v>
+        <v>0.3523</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3825</v>
+        <v>0.026</v>
       </c>
       <c r="V10" t="n">
         <v>1.2186</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4539</v>
+        <v>-1.1427</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8796</v>
+        <v>-1.6773</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4257</v>
+        <v>0.5346</v>
       </c>
       <c r="G11" t="n">
         <v>0.2506</v>
@@ -1312,13 +1312,13 @@
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4859</v>
+        <v>-0.1747</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2888</v>
+        <v>-0.0866</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.197</v>
+        <v>-0.0881</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2186</v>
@@ -1348,10 +1348,10 @@
         <v>33.95230000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>23.5335</v>
+        <v>23.5332</v>
       </c>
       <c r="F12" t="n">
-        <v>10.4189</v>
+        <v>10.4188</v>
       </c>
       <c r="G12" t="n">
         <v>26.5104</v>
@@ -1360,7 +1360,7 @@
         <v>23.812</v>
       </c>
       <c r="I12" t="n">
-        <v>2.698500000000001</v>
+        <v>2.6985</v>
       </c>
       <c r="J12" t="n">
         <v>25.663</v>
@@ -1369,7 +1369,7 @@
         <v>21.6103</v>
       </c>
       <c r="L12" t="n">
-        <v>4.0526</v>
+        <v>4.052600000000001</v>
       </c>
       <c r="M12" t="n">
         <v>0.8473999999999996</v>
@@ -1390,13 +1390,13 @@
         <v>12.6973</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1639</v>
+        <v>3.1638</v>
       </c>
       <c r="T12" t="n">
         <v>2.4084</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7556</v>
+        <v>0.7556000000000002</v>
       </c>
       <c r="V12" t="n">
         <v>2.3246</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8904</v>
+        <v>-0.1683</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9113</v>
+        <v>2.4169</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8017</v>
+        <v>-2.5851</v>
       </c>
       <c r="G13" t="n">
         <v>0.4829</v>
@@ -1468,13 +1468,13 @@
         <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.522</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9684</v>
+        <v>-0.4628</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5537</v>
+        <v>-0.3372</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2186</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.7726</v>
+        <v>-1.3299</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0525</v>
+        <v>-2.5795</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.8251</v>
+        <v>1.2496</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.4452</v>
+        <v>-1.4786</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.339</v>
+        <v>-1.2087</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.1062</v>
+        <v>-0.2698</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0538</v>
+        <v>-0.9798</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9452</v>
+        <v>-0.3057</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1086</v>
+        <v>-0.6741</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.499</v>
+        <v>-0.4988</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.2842</v>
+        <v>-0.903</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2148</v>
+        <v>0.4043</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3275</v>
+        <v>0.1802</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.22</v>
+        <v>-0.2008</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1075</v>
+        <v>0.381</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.8965</v>
+        <v>-2.0801</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.984</v>
+        <v>2.1536</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0876</v>
+        <v>-4.2336</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4786</v>
+        <v>-3.4452</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.2087</v>
+        <v>-2.339</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2698</v>
+        <v>-1.1062</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9798</v>
+        <v>1.0538</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3057</v>
+        <v>0.9452</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6741</v>
+        <v>0.1086</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4988</v>
+        <v>-4.499</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.903</v>
+        <v>-3.2842</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4043</v>
+        <v>-1.2148</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3863</v>
+        <v>-0.6349</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6052</v>
+        <v>-0.1189</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2189</v>
+        <v>-0.516</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.8558</v>
+        <v>-2.612</v>
       </c>
       <c r="E16" t="n">
         <v>-0.7327</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1232</v>
+        <v>-1.8794</v>
       </c>
       <c r="G16" t="n">
         <v>-3.4072</v>
@@ -1702,13 +1702,13 @@
         <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4253</v>
+        <v>-0.1816</v>
       </c>
       <c r="T16" t="n">
         <v>0.0083</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4337</v>
+        <v>-0.1899</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.6351</v>
+        <v>-3.7168</v>
       </c>
       <c r="E17" t="n">
         <v>-1.2587</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3764</v>
+        <v>-2.4581</v>
       </c>
       <c r="G17" t="n">
         <v>-2.5007</v>
@@ -1780,13 +1780,13 @@
         <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2014</v>
+        <v>0.1197</v>
       </c>
       <c r="T17" t="n">
         <v>0.3247</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1233</v>
+        <v>-0.205</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5545</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.0808</v>
+        <v>-4.1142</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.8097</v>
+        <v>-0.9106</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2711</v>
+        <v>-3.2036</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.0239</v>
+        <v>-2.2772</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.1203</v>
+        <v>-1.1039</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-1.1733</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.3669</v>
+        <v>-0.0159</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0591</v>
+        <v>1.2919</v>
       </c>
       <c r="L18" t="n">
         <v>-1.3077</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6571</v>
+        <v>-2.2613</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.0611</v>
+        <v>-2.3958</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4041</v>
+        <v>0.1344</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-1.9534</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3421</v>
+        <v>-0.9189000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9329</v>
+        <v>-0.3823</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4093</v>
+        <v>-0.5366</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5545</v>
+        <v>-0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5545</v>
+        <v>1.441</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.3574</v>
+        <v>-4.4476</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6161</v>
+        <v>0.7331</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.7412</v>
+        <v>-5.1807</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.0103</v>
+        <v>-1.7658</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.7018</v>
+        <v>-2.4403</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3085</v>
+        <v>0.6745</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.8645</v>
+        <v>1.6447</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3661</v>
+        <v>-0.2443</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4984</v>
+        <v>1.8891</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.1457</v>
+        <v>-3.4105</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.3356</v>
+        <v>-2.196</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8101</v>
+        <v>-1.2146</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1105</v>
+        <v>-0.5571</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1282</v>
+        <v>-0.2475</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0177</v>
+        <v>-0.3096</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4959</v>
+        <v>-3.1014</v>
       </c>
       <c r="W19" t="n">
-        <v>2.0503</v>
+        <v>-0.6642</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5545</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4952</v>
+        <v>-4.6235</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1671</v>
+        <v>-1.2682</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.328</v>
+        <v>-3.3553</v>
       </c>
       <c r="G20" t="n">
         <v>-3.0844</v>
@@ -2014,13 +2014,13 @@
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.274</v>
+        <v>-0.4024</v>
       </c>
       <c r="T20" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.0185</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3567</v>
+        <v>-0.3839</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9414</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8169</v>
+        <v>-5.0466</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3151</v>
+        <v>-4.7197</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5018</v>
+        <v>-0.3269</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2772</v>
+        <v>-4.0239</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1039</v>
+        <v>-3.1203</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1733</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0159</v>
+        <v>-2.3669</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2919</v>
+        <v>-1.0591</v>
       </c>
       <c r="L21" t="n">
         <v>-1.3077</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2613</v>
+        <v>-1.6571</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.3958</v>
+        <v>-2.0611</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1344</v>
+        <v>0.4041</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.586</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6216</v>
+        <v>0.3763</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.0229</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8348</v>
+        <v>0.3534</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3321</v>
+        <v>0.5545</v>
       </c>
       <c r="W21" t="n">
-        <v>1.441</v>
+        <v>0.5545</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1517</v>
+        <v>-5.139</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3286</v>
+        <v>-2.425</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.4803</v>
+        <v>-2.714</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7658</v>
+        <v>-5.0103</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4403</v>
+        <v>-3.7018</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6745</v>
+        <v>-1.3085</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6447</v>
+        <v>-1.8645</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2443</v>
+        <v>-1.3661</v>
       </c>
       <c r="L22" t="n">
-        <v>1.8891</v>
+        <v>-0.4984</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.4105</v>
+        <v>-3.1457</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.196</v>
+        <v>-2.3356</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2146</v>
+        <v>-0.8101</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2612</v>
+        <v>0.3288</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.652</v>
+        <v>0.3193</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6092</v>
+        <v>0.0095</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.1014</v>
+        <v>1.4959</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>2.0503</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-33.9524</v>
+        <v>-33.27800000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.590999999999999</v>
+        <v>-8.590799999999998</v>
       </c>
       <c r="F23" t="n">
-        <v>-25.3612</v>
+        <v>-24.6871</v>
       </c>
       <c r="G23" t="n">
         <v>-26.5104</v>
@@ -2221,7 +2221,7 @@
         <v>-2.6984</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8474999999999999</v>
+        <v>-0.8475000000000001</v>
       </c>
       <c r="K23" t="n">
         <v>-2.2014</v>
@@ -2239,7 +2239,7 @@
         <v>-4.0526</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.953299999999999</v>
+        <v>-1.9533</v>
       </c>
       <c r="Q23" t="n">
         <v>-12.6971</v>
@@ -2248,13 +2248,13 @@
         <v>10.7439</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.1639</v>
+        <v>-2.4898</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7557000000000003</v>
+        <v>-0.7556</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.4084</v>
+        <v>-1.7343</v>
       </c>
       <c r="V23" t="n">
         <v>-2.3245</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484334_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484334_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.7731</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1864</v>
+        <v>4.0163</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5609</v>
+        <v>1.4432</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3745</v>
+        <v>2.5731</v>
       </c>
       <c r="G5" t="n">
-        <v>2.716</v>
+        <v>4.5006</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9182</v>
+        <v>3.8402</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2021</v>
+        <v>0.6605</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9452</v>
+        <v>2.8229</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6631</v>
+        <v>2.7015</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2821</v>
+        <v>0.1214</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2291</v>
+        <v>1.6778</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2551</v>
+        <v>1.1387</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4842</v>
+        <v>0.5391</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6341</v>
+        <v>-0.1252</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3385</v>
+        <v>-0.2077</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2956</v>
+        <v>0.0824</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0549</v>
+        <v>-0.5545</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2224</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +902,72 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.0163</v>
+        <v>3.5724</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4432</v>
+        <v>3.9469</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5731</v>
+        <v>-0.3745</v>
       </c>
       <c r="G6" t="n">
-        <v>4.5006</v>
+        <v>2.1021</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8402</v>
+        <v>2.3042</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6605</v>
+        <v>-0.2021</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8229</v>
+        <v>3.3312</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7015</v>
+        <v>2.0491</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1214</v>
+        <v>1.2821</v>
       </c>
       <c r="M6" t="n">
-        <v>1.6778</v>
+        <v>-1.2291</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1387</v>
+        <v>0.2551</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5391</v>
+        <v>-1.4842</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1252</v>
+        <v>0.6341</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2077</v>
+        <v>0.3385</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0824</v>
+        <v>0.2956</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5545</v>
+        <v>0.0549</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5545</v>
+        <v>-0.2224</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.4996</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.3869</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,11 +1213,16 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5609</v>
+        <v>0.614</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8129</v>
+        <v>0.614</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2519</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7904</v>
+        <v>0.614</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0834</v>
+        <v>0.614</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8739</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4304</v>
+        <v>0.614</v>
       </c>
       <c r="K10" t="n">
-        <v>0.903</v>
+        <v>0.614</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3334</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3601</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1804</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5405</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3783</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3523</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1427</v>
+        <v>-0.5609</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6773</v>
+        <v>-0.8129</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5346</v>
+        <v>0.2519</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2506</v>
+        <v>-0.7904</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0747</v>
+        <v>1.0834</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1759</v>
+        <v>-1.8739</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4187</v>
+        <v>-0.4304</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3249</v>
+        <v>0.903</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-1.3334</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6692</v>
+        <v>-0.3601</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3996</v>
+        <v>0.1804</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2696</v>
+        <v>-0.5405</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1747</v>
+        <v>0.3783</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0866</v>
+        <v>0.3523</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0881</v>
+        <v>0.026</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2186</v>
+        <v>1.2186</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,151 +1400,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>33.95230000000001</v>
+        <v>-1.1427</v>
       </c>
       <c r="E12" t="n">
-        <v>23.5332</v>
+        <v>-1.6773</v>
       </c>
       <c r="F12" t="n">
-        <v>10.4188</v>
+        <v>0.5346</v>
       </c>
       <c r="G12" t="n">
-        <v>26.5104</v>
+        <v>0.2506</v>
       </c>
       <c r="H12" t="n">
-        <v>23.812</v>
+        <v>0.0747</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6985</v>
+        <v>0.1759</v>
       </c>
       <c r="J12" t="n">
-        <v>25.663</v>
+        <v>-0.4187</v>
       </c>
       <c r="K12" t="n">
-        <v>21.6103</v>
+        <v>-0.3249</v>
       </c>
       <c r="L12" t="n">
-        <v>4.052600000000001</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8473999999999996</v>
+        <v>0.6692</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2016</v>
+        <v>0.3996</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3541</v>
+        <v>0.2696</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9535</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-10.7438</v>
+        <v>-1.1721</v>
       </c>
       <c r="R12" t="n">
-        <v>12.6973</v>
+        <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1638</v>
+        <v>-0.1747</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4084</v>
+        <v>-0.0866</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7556000000000002</v>
+        <v>-0.0881</v>
       </c>
       <c r="V12" t="n">
-        <v>2.3246</v>
+        <v>-1.2186</v>
       </c>
       <c r="W12" t="n">
-        <v>6.2057</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.8813</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1683</v>
+        <v>33.9523</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4169</v>
+        <v>23.5332</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5851</v>
+        <v>10.4188</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4829</v>
+        <v>26.5105</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7698</v>
+        <v>23.812</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2527</v>
+        <v>2.6985</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8796</v>
+        <v>25.663</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4912</v>
+        <v>21.6103</v>
       </c>
       <c r="L13" t="n">
-        <v>2.3885</v>
+        <v>4.052600000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.3967</v>
+        <v>0.8473999999999996</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.2609</v>
+        <v>2.2016</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1358</v>
+        <v>-1.3541</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3674</v>
+        <v>1.9535</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-10.7438</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3674</v>
+        <v>12.6973</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7999000000000001</v>
+        <v>3.1638</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4628</v>
+        <v>2.4084</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3372</v>
+        <v>0.7555999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2186</v>
+        <v>2.3246</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>6.2057</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2186</v>
-      </c>
+        <v>-3.8813</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.3299</v>
+        <v>0.307</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.5795</v>
+        <v>0.307</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2496</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.4786</v>
+        <v>0.307</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.2087</v>
+        <v>0.307</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2698</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9798</v>
+        <v>0.307</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3057</v>
+        <v>0.307</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4988</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.903</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4043</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1802</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2008</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.381</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.0801</v>
+        <v>-0.1683</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1536</v>
+        <v>2.4169</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.2336</v>
+        <v>-2.5851</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.4452</v>
+        <v>0.4829</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.339</v>
+        <v>-1.7698</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1062</v>
+        <v>2.2527</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0538</v>
+        <v>2.8796</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9452</v>
+        <v>0.4912</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1086</v>
+        <v>2.3885</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.499</v>
+        <v>-2.3967</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.2842</v>
+        <v>-2.2609</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2148</v>
+        <v>-0.1358</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6349</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1189</v>
+        <v>-0.4628</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.516</v>
+        <v>-0.3372</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2186</v>
+        <v>-1.2186</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.612</v>
+        <v>-1.3299</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7327</v>
+        <v>-2.5795</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8794</v>
+        <v>1.2496</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.4072</v>
+        <v>-1.4786</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.3282</v>
+        <v>-1.2087</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.079</v>
+        <v>-0.2698</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.9596</v>
+        <v>-0.9798</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.3057</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3482</v>
+        <v>-0.6741</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4476</v>
+        <v>-0.4988</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7168</v>
+        <v>-0.903</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2692</v>
+        <v>0.4043</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9767</v>
+        <v>-0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1816</v>
+        <v>0.1802</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0083</v>
+        <v>-0.2008</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1899</v>
+        <v>0.381</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.7168</v>
+        <v>-2.0801</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2587</v>
+        <v>2.1536</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4581</v>
+        <v>-4.2336</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.5007</v>
+        <v>-3.4452</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.9069</v>
+        <v>-2.339</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5938</v>
+        <v>-1.1062</v>
       </c>
       <c r="J17" t="n">
-        <v>0.37</v>
+        <v>1.0538</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2891</v>
+        <v>0.9452</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0809</v>
+        <v>0.1086</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8707</v>
+        <v>-4.499</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.196</v>
+        <v>-3.2842</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6747</v>
+        <v>-1.2148</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1197</v>
+        <v>-0.6349</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3247</v>
+        <v>-0.1189</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.205</v>
+        <v>-0.516</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.1142</v>
+        <v>-2.612</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9106</v>
+        <v>-0.7327</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2036</v>
+        <v>-1.8794</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2772</v>
+        <v>-3.4072</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1039</v>
+        <v>-2.3282</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1733</v>
+        <v>-1.079</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0159</v>
+        <v>-1.9596</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2919</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3077</v>
+        <v>-1.3482</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2613</v>
+        <v>-1.4476</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.3958</v>
+        <v>-1.7168</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1344</v>
+        <v>0.2692</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.1816</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3823</v>
+        <v>0.0083</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5366</v>
+        <v>-0.1899</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.441</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7731</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.4476</v>
+        <v>-3.7168</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7331</v>
+        <v>-1.2587</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.1807</v>
+        <v>-2.4581</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7658</v>
+        <v>-2.5007</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.4403</v>
+        <v>-1.9069</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6745</v>
+        <v>-0.5938</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6447</v>
+        <v>0.37</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2443</v>
+        <v>0.2891</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8891</v>
+        <v>0.0809</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.4105</v>
+        <v>-2.8707</v>
       </c>
       <c r="N19" t="n">
         <v>-2.196</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2146</v>
+        <v>-0.6747</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5571</v>
+        <v>0.1197</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2475</v>
+        <v>0.3247</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3096</v>
+        <v>-0.205</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.1014</v>
+        <v>-0.5545</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4373</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.6235</v>
+        <v>-4.1142</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2682</v>
+        <v>-0.9106</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3553</v>
+        <v>-3.2036</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0844</v>
+        <v>-2.2772</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.8931</v>
+        <v>-1.1039</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8087</v>
+        <v>-1.1733</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3911</v>
+        <v>-0.0159</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.6322</v>
+        <v>1.2919</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0233</v>
+        <v>-1.3077</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.4755</v>
+        <v>-2.2613</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2609</v>
+        <v>-2.3958</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2146</v>
+        <v>0.1344</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4024</v>
+        <v>-0.9189000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0185</v>
+        <v>-0.3823</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3839</v>
+        <v>-0.5366</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9414</v>
+        <v>-0.3321</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6642</v>
+        <v>1.441</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0466</v>
+        <v>-4.4476</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.7197</v>
+        <v>0.7331</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3269</v>
+        <v>-5.1807</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.0239</v>
+        <v>-1.7658</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.1203</v>
+        <v>-2.4403</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9036999999999999</v>
+        <v>0.6745</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3669</v>
+        <v>1.6447</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0591</v>
+        <v>-0.2443</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3077</v>
+        <v>1.8891</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6571</v>
+        <v>-3.4105</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0611</v>
+        <v>-2.196</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4041</v>
+        <v>-1.2146</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3763</v>
+        <v>-0.5571</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0229</v>
+        <v>-0.2475</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3534</v>
+        <v>-0.3096</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5545</v>
+        <v>-3.1014</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5545</v>
+        <v>-0.6642</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.139</v>
+        <v>-4.6235</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.425</v>
+        <v>-1.2682</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.714</v>
+        <v>-3.3553</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.0103</v>
+        <v>-3.0844</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.7018</v>
+        <v>-3.8931</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3085</v>
+        <v>0.8087</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8645</v>
+        <v>0.3911</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3661</v>
+        <v>-1.6322</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4984</v>
+        <v>2.0233</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.1457</v>
+        <v>-3.4755</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.3356</v>
+        <v>-2.2609</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8101</v>
+        <v>-1.2146</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3288</v>
+        <v>-0.4024</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3193</v>
+        <v>-0.0185</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0095</v>
+        <v>-0.3839</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4959</v>
+        <v>-0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>2.0503</v>
+        <v>-0.6642</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,235 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-5.139</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.425</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-2.714</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-5.0103</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-3.7018</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.3085</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.8645</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1.3661</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.4984</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-3.1457</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-2.3356</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.8101</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.0503</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>G. VINALLONGA BLANCO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-5.3536</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-5.0267</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.3269</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-4.3309</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-3.4273</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.9036999999999999</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-2.6739</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.3661</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.3077</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.6571</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-2.0611</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484334_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>-33.27800000000001</v>
       </c>
-      <c r="E23" t="n">
-        <v>-8.590799999999998</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="E25" t="n">
+        <v>-8.5908</v>
+      </c>
+      <c r="F25" t="n">
         <v>-24.6871</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G25" t="n">
         <v>-26.5104</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H25" t="n">
         <v>-23.812</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I25" t="n">
         <v>-2.6984</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J25" t="n">
         <v>-0.8475000000000001</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K25" t="n">
         <v>-2.2014</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.3543</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="L25" t="n">
+        <v>1.354299999999999</v>
+      </c>
+      <c r="M25" t="n">
         <v>-25.6629</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N25" t="n">
         <v>-21.6103</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O25" t="n">
         <v>-4.0526</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P25" t="n">
         <v>-1.9533</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q25" t="n">
         <v>-12.6971</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>10.7439</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>-2.4898</v>
       </c>
-      <c r="T23" t="n">
-        <v>-0.7556</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="T25" t="n">
+        <v>-0.7555999999999999</v>
+      </c>
+      <c r="U25" t="n">
         <v>-1.7343</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V25" t="n">
         <v>-2.3245</v>
       </c>
-      <c r="W23" t="n">
-        <v>5.709099999999999</v>
-      </c>
-      <c r="X23" t="n">
+      <c r="W25" t="n">
+        <v>5.7091</v>
+      </c>
+      <c r="X25" t="n">
         <v>-8.033799999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
